--- a/output/Distribution Configuration.xlsx
+++ b/output/Distribution Configuration.xlsx
@@ -29828,18 +29828,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19.2" customWidth="1" min="1" max="1"/>
-    <col width="13.2" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15.6" customWidth="1" min="4" max="4"/>
-    <col width="7.199999999999999" customWidth="1" min="5" max="5"/>
-    <col width="14.4" customWidth="1" min="6" max="6"/>
-    <col width="14.4" customWidth="1" min="7" max="7"/>
-    <col width="44.4" customWidth="1" min="8" max="8"/>
-    <col width="19.2" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19.2" customWidth="1" min="2" max="2"/>
+    <col width="13.2" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15.6" customWidth="1" min="5" max="5"/>
+    <col width="7.199999999999999" customWidth="1" min="6" max="6"/>
+    <col width="26.4" customWidth="1" min="7" max="7"/>
+    <col width="26.4" customWidth="1" min="8" max="8"/>
+    <col width="26.4" customWidth="1" min="9" max="9"/>
+    <col width="26.4" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -29866,92 +29867,102 @@
     <row r="5">
       <c r="A5" s="25" t="inlineStr">
         <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
           <t>Constant value</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Key value</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>Language</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
-        <is>
-          <t>Terms text</t>
-        </is>
-      </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>Terms text</t>
+          <t>Reference field TEL1</t>
         </is>
       </c>
       <c r="H5" s="25" t="inlineStr">
         <is>
-          <t>Transport method - trade stat (TST)</t>
+          <t>Reference field TEL2</t>
         </is>
       </c>
       <c r="I5" s="25" t="inlineStr">
         <is>
-          <t>Container used</t>
+          <t>Reference field VRDL</t>
+        </is>
+      </c>
+      <c r="J5" s="25" t="inlineStr">
+        <is>
+          <t>Reference field COTT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="inlineStr">
         <is>
+          <t>DIVI</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
           <t>STCO</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>STKY</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>LNCD</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>TX40</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="F6" s="26" t="inlineStr">
         <is>
           <t>TX15</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="G6" s="26" t="inlineStr">
         <is>
           <t>TEL1</t>
         </is>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="H6" s="26" t="inlineStr">
         <is>
           <t>TEL2</t>
         </is>
       </c>
-      <c r="H6" s="26" t="inlineStr">
+      <c r="I6" s="26" t="inlineStr">
         <is>
           <t>VRDL</t>
         </is>
       </c>
-      <c r="I6" s="26" t="inlineStr">
+      <c r="J6" s="26" t="inlineStr">
         <is>
           <t>COTT</t>
         </is>
@@ -29995,10 +30006,15 @@
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I7" s="27" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I7" s="27" t="inlineStr">
+      <c r="J7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -30007,39 +30023,44 @@
     <row r="8">
       <c r="A8" s="28" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>15</t>
         </is>
-      </c>
-      <c r="F8" s="28" t="n">
-        <v>36</v>
       </c>
       <c r="G8" s="28" t="n">
         <v>36</v>
       </c>
       <c r="H8" s="28" t="n">
+        <v>36</v>
+      </c>
+      <c r="I8" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="I8" s="28" t="n">
+      <c r="J8" s="28" t="n">
         <v>1</v>
       </c>
     </row>
@@ -30057,42 +30078,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG8"/>
+  <dimension ref="A1:AH8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14.4" customWidth="1" min="1" max="1"/>
-    <col width="8.4" customWidth="1" min="2" max="2"/>
-    <col width="15.6" customWidth="1" min="3" max="3"/>
-    <col width="7.199999999999999" customWidth="1" min="4" max="4"/>
-    <col width="15.6" customWidth="1" min="5" max="5"/>
-    <col width="21.6" customWidth="1" min="6" max="6"/>
-    <col width="8.4" customWidth="1" min="7" max="7"/>
-    <col width="39.6" customWidth="1" min="8" max="8"/>
-    <col width="45.6" customWidth="1" min="9" max="9"/>
-    <col width="46.8" customWidth="1" min="10" max="10"/>
-    <col width="49.2" customWidth="1" min="11" max="11"/>
-    <col width="21.6" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14.4" customWidth="1" min="2" max="2"/>
+    <col width="8.4" customWidth="1" min="3" max="3"/>
+    <col width="15.6" customWidth="1" min="4" max="4"/>
+    <col width="7.199999999999999" customWidth="1" min="5" max="5"/>
+    <col width="15.6" customWidth="1" min="6" max="6"/>
+    <col width="21.6" customWidth="1" min="7" max="7"/>
+    <col width="8.4" customWidth="1" min="8" max="8"/>
+    <col width="39.6" customWidth="1" min="9" max="9"/>
+    <col width="45.6" customWidth="1" min="10" max="10"/>
+    <col width="46.8" customWidth="1" min="11" max="11"/>
+    <col width="49.2" customWidth="1" min="12" max="12"/>
     <col width="21.6" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="43.2" customWidth="1" min="15" max="15"/>
-    <col width="49.2" customWidth="1" min="16" max="16"/>
-    <col width="34.8" customWidth="1" min="17" max="17"/>
-    <col width="45.6" customWidth="1" min="18" max="18"/>
-    <col width="34.8" customWidth="1" min="19" max="19"/>
-    <col width="21.6" customWidth="1" min="20" max="20"/>
-    <col width="22.8" customWidth="1" min="21" max="21"/>
-    <col width="31.2" customWidth="1" min="22" max="22"/>
-    <col width="26.4" customWidth="1" min="23" max="23"/>
-    <col width="15.6" customWidth="1" min="24" max="24"/>
-    <col width="21.6" customWidth="1" min="25" max="25"/>
-    <col width="31.2" customWidth="1" min="26" max="26"/>
-    <col width="20.4" customWidth="1" min="27" max="27"/>
-    <col width="32.4" customWidth="1" min="28" max="28"/>
-    <col width="25.2" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
-    <col width="18" customWidth="1" min="31" max="31"/>
-    <col width="21.6" customWidth="1" min="32" max="32"/>
-    <col width="13.2" customWidth="1" min="33" max="33"/>
+    <col width="21.6" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
+    <col width="43.2" customWidth="1" min="16" max="16"/>
+    <col width="49.2" customWidth="1" min="17" max="17"/>
+    <col width="34.8" customWidth="1" min="18" max="18"/>
+    <col width="45.6" customWidth="1" min="19" max="19"/>
+    <col width="34.8" customWidth="1" min="20" max="20"/>
+    <col width="21.6" customWidth="1" min="21" max="21"/>
+    <col width="22.8" customWidth="1" min="22" max="22"/>
+    <col width="31.2" customWidth="1" min="23" max="23"/>
+    <col width="26.4" customWidth="1" min="24" max="24"/>
+    <col width="15.6" customWidth="1" min="25" max="25"/>
+    <col width="21.6" customWidth="1" min="26" max="26"/>
+    <col width="31.2" customWidth="1" min="27" max="27"/>
+    <col width="20.4" customWidth="1" min="28" max="28"/>
+    <col width="32.4" customWidth="1" min="29" max="29"/>
+    <col width="25.2" customWidth="1" min="30" max="30"/>
+    <col width="12" customWidth="1" min="31" max="31"/>
+    <col width="18" customWidth="1" min="32" max="32"/>
+    <col width="21.6" customWidth="1" min="33" max="33"/>
+    <col width="13.2" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30119,165 +30141,170 @@
     <row r="5">
       <c r="A5" s="25" t="inlineStr">
         <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
           <t>Route type</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Responsible</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>Place of loading</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
         <is>
           <t>Place</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t>Transportation planning horizon</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="J5" s="25" t="inlineStr">
         <is>
           <t>Stipulated internal lead time - days</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t>Stipulated internal lead time - hours</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="L5" s="25" t="inlineStr">
         <is>
           <t>Stipulated internal lead time - minutes</t>
         </is>
       </c>
-      <c r="L5" s="25" t="inlineStr">
+      <c r="M5" s="25" t="inlineStr">
         <is>
           <t>Days to deadline</t>
         </is>
       </c>
-      <c r="M5" s="25" t="inlineStr">
+      <c r="N5" s="25" t="inlineStr">
         <is>
           <t>Deadline - hours</t>
         </is>
       </c>
-      <c r="N5" s="25" t="inlineStr">
+      <c r="O5" s="25" t="inlineStr">
         <is>
           <t>Deadline - minutes</t>
         </is>
       </c>
-      <c r="O5" s="25" t="inlineStr">
+      <c r="P5" s="25" t="inlineStr">
         <is>
           <t>Manual shipment scheduling allowed</t>
         </is>
       </c>
-      <c r="P5" s="25" t="inlineStr">
+      <c r="Q5" s="25" t="inlineStr">
         <is>
           <t>Ignore deadline when connecting dely no</t>
         </is>
       </c>
-      <c r="Q5" s="25" t="inlineStr">
+      <c r="R5" s="25" t="inlineStr">
         <is>
           <t>Automatic shipment creation</t>
         </is>
       </c>
-      <c r="R5" s="25" t="inlineStr">
+      <c r="S5" s="25" t="inlineStr">
         <is>
           <t>Automatic creation of delivery order</t>
         </is>
       </c>
-      <c r="S5" s="25" t="inlineStr">
+      <c r="T5" s="25" t="inlineStr">
         <is>
           <t>Responsible must be entered</t>
         </is>
       </c>
-      <c r="T5" s="25" t="inlineStr">
+      <c r="U5" s="25" t="inlineStr">
         <is>
           <t>Loading platform</t>
         </is>
       </c>
-      <c r="U5" s="25" t="inlineStr">
+      <c r="V5" s="25" t="inlineStr">
         <is>
           <t>Time of departure</t>
         </is>
       </c>
-      <c r="V5" s="25" t="inlineStr">
+      <c r="W5" s="25" t="inlineStr">
         <is>
           <t>Transportation equipment</t>
         </is>
       </c>
-      <c r="W5" s="25" t="inlineStr">
+      <c r="X5" s="25" t="inlineStr">
         <is>
           <t>Check capacity alarm</t>
         </is>
       </c>
-      <c r="X5" s="25" t="inlineStr">
+      <c r="Y5" s="25" t="inlineStr">
         <is>
           <t>GUI picture</t>
         </is>
       </c>
-      <c r="Y5" s="25" t="inlineStr">
+      <c r="Z5" s="25" t="inlineStr">
         <is>
           <t>Forwarding agent</t>
         </is>
       </c>
-      <c r="Z5" s="25" t="inlineStr">
+      <c r="AA5" s="25" t="inlineStr">
         <is>
           <t>Transportation equipment</t>
         </is>
       </c>
-      <c r="AA5" s="25" t="inlineStr">
+      <c r="AB5" s="25" t="inlineStr">
         <is>
           <t>Delivery method</t>
         </is>
       </c>
-      <c r="AB5" s="25" t="inlineStr">
+      <c r="AC5" s="25" t="inlineStr">
         <is>
           <t>Transportation service ID</t>
         </is>
       </c>
-      <c r="AC5" s="25" t="inlineStr">
+      <c r="AD5" s="25" t="inlineStr">
         <is>
           <t>Number of kilometer</t>
         </is>
       </c>
-      <c r="AD5" s="25" t="inlineStr">
+      <c r="AE5" s="25" t="inlineStr">
         <is>
           <t>Customer</t>
         </is>
       </c>
-      <c r="AE5" s="25" t="inlineStr">
+      <c r="AF5" s="25" t="inlineStr">
         <is>
           <t>Load building</t>
         </is>
       </c>
-      <c r="AF5" s="25" t="inlineStr">
+      <c r="AG5" s="25" t="inlineStr">
         <is>
           <t>Loading platform</t>
         </is>
       </c>
-      <c r="AG5" s="25" t="inlineStr">
+      <c r="AH5" s="25" t="inlineStr">
         <is>
           <t>Direction</t>
         </is>
@@ -30286,165 +30313,170 @@
     <row r="6">
       <c r="A6" s="26" t="inlineStr">
         <is>
+          <t>DIVI</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
           <t>RUTP</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>ROUT</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>TX40</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>TX15</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="F6" s="26" t="inlineStr">
         <is>
           <t>RESP</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="G6" s="26" t="inlineStr">
         <is>
           <t>SDES</t>
         </is>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="H6" s="26" t="inlineStr">
         <is>
           <t>EDES</t>
         </is>
       </c>
-      <c r="H6" s="26" t="inlineStr">
+      <c r="I6" s="26" t="inlineStr">
         <is>
           <t>TPHO</t>
         </is>
       </c>
-      <c r="I6" s="26" t="inlineStr">
+      <c r="J6" s="26" t="inlineStr">
         <is>
           <t>SILD</t>
         </is>
       </c>
-      <c r="J6" s="26" t="inlineStr">
+      <c r="K6" s="26" t="inlineStr">
         <is>
           <t>SILH</t>
         </is>
       </c>
-      <c r="K6" s="26" t="inlineStr">
+      <c r="L6" s="26" t="inlineStr">
         <is>
           <t>SILM</t>
         </is>
       </c>
-      <c r="L6" s="26" t="inlineStr">
+      <c r="M6" s="26" t="inlineStr">
         <is>
           <t>LILD</t>
         </is>
       </c>
-      <c r="M6" s="26" t="inlineStr">
+      <c r="N6" s="26" t="inlineStr">
         <is>
           <t>LILH</t>
         </is>
       </c>
-      <c r="N6" s="26" t="inlineStr">
+      <c r="O6" s="26" t="inlineStr">
         <is>
           <t>LILM</t>
         </is>
       </c>
-      <c r="O6" s="26" t="inlineStr">
+      <c r="P6" s="26" t="inlineStr">
         <is>
           <t>DLMC</t>
         </is>
       </c>
-      <c r="P6" s="26" t="inlineStr">
+      <c r="Q6" s="26" t="inlineStr">
         <is>
           <t>DLAC</t>
         </is>
       </c>
-      <c r="Q6" s="26" t="inlineStr">
+      <c r="R6" s="26" t="inlineStr">
         <is>
           <t>ACNC</t>
         </is>
       </c>
-      <c r="R6" s="26" t="inlineStr">
+      <c r="S6" s="26" t="inlineStr">
         <is>
           <t>ACDO</t>
         </is>
       </c>
-      <c r="S6" s="26" t="inlineStr">
+      <c r="T6" s="26" t="inlineStr">
         <is>
           <t>MARE</t>
         </is>
       </c>
-      <c r="T6" s="26" t="inlineStr">
+      <c r="U6" s="26" t="inlineStr">
         <is>
           <t>MALP</t>
         </is>
       </c>
-      <c r="U6" s="26" t="inlineStr">
+      <c r="V6" s="26" t="inlineStr">
         <is>
           <t>MADE</t>
         </is>
       </c>
-      <c r="V6" s="26" t="inlineStr">
+      <c r="W6" s="26" t="inlineStr">
         <is>
           <t>MACA</t>
         </is>
       </c>
-      <c r="W6" s="26" t="inlineStr">
+      <c r="X6" s="26" t="inlineStr">
         <is>
           <t>CCCA</t>
         </is>
       </c>
-      <c r="X6" s="26" t="inlineStr">
+      <c r="Y6" s="26" t="inlineStr">
         <is>
           <t>PINO</t>
         </is>
       </c>
-      <c r="Y6" s="26" t="inlineStr">
+      <c r="Z6" s="26" t="inlineStr">
         <is>
           <t>FWNO</t>
         </is>
       </c>
-      <c r="Z6" s="26" t="inlineStr">
+      <c r="AA6" s="26" t="inlineStr">
         <is>
           <t>TRCA</t>
         </is>
       </c>
-      <c r="AA6" s="26" t="inlineStr">
+      <c r="AB6" s="26" t="inlineStr">
         <is>
           <t>MODL</t>
         </is>
       </c>
-      <c r="AB6" s="26" t="inlineStr">
+      <c r="AC6" s="26" t="inlineStr">
         <is>
           <t>TSID</t>
         </is>
       </c>
-      <c r="AC6" s="26" t="inlineStr">
+      <c r="AD6" s="26" t="inlineStr">
         <is>
           <t>DIST</t>
         </is>
       </c>
-      <c r="AD6" s="26" t="inlineStr">
+      <c r="AE6" s="26" t="inlineStr">
         <is>
           <t>CUNO</t>
         </is>
       </c>
-      <c r="AE6" s="26" t="inlineStr">
+      <c r="AF6" s="26" t="inlineStr">
         <is>
           <t>LOBL</t>
         </is>
       </c>
-      <c r="AF6" s="26" t="inlineStr">
+      <c r="AG6" s="26" t="inlineStr">
         <is>
           <t>LODO</t>
         </is>
       </c>
-      <c r="AG6" s="26" t="inlineStr">
+      <c r="AH6" s="26" t="inlineStr">
         <is>
           <t>INOU</t>
         </is>
@@ -30453,165 +30485,170 @@
     <row r="7">
       <c r="A7" s="27" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="B7" s="27" t="inlineStr">
+      <c r="C7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="F7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F7" s="27" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G7" s="27" t="inlineStr">
+      <c r="H7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="H7" s="27" t="inlineStr">
+      <c r="I7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I7" s="27" t="inlineStr">
+      <c r="J7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="J7" s="27" t="inlineStr">
+      <c r="K7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K7" s="27" t="inlineStr">
+      <c r="L7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L7" s="27" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M7" s="27" t="inlineStr">
+      <c r="N7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="N7" s="27" t="inlineStr">
+      <c r="O7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="O7" s="27" t="inlineStr">
+      <c r="P7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P7" s="27" t="inlineStr">
+      <c r="Q7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q7" s="27" t="inlineStr">
+      <c r="R7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R7" s="27" t="inlineStr">
+      <c r="S7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="S7" s="27" t="inlineStr">
+      <c r="T7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="T7" s="27" t="inlineStr">
+      <c r="U7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="U7" s="27" t="inlineStr">
+      <c r="V7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="V7" s="27" t="inlineStr">
+      <c r="W7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="W7" s="27" t="inlineStr">
+      <c r="X7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="X7" s="27" t="inlineStr">
+      <c r="Y7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Y7" s="27" t="inlineStr">
+      <c r="Z7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="Z7" s="27" t="inlineStr">
+      <c r="AA7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="AA7" s="27" t="inlineStr">
+      <c r="AB7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="AB7" s="27" t="inlineStr">
+      <c r="AC7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="AC7" s="27" t="inlineStr">
+      <c r="AD7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AD7" s="27" t="inlineStr">
+      <c r="AE7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="AE7" s="27" t="inlineStr">
+      <c r="AF7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AF7" s="27" t="inlineStr">
+      <c r="AG7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="AG7" s="27" t="inlineStr">
+      <c r="AH7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -30620,165 +30657,170 @@
     <row r="8">
       <c r="A8" s="28" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="G8" s="28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G8" s="28" t="inlineStr">
+      <c r="H8" s="28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="H8" s="28" t="inlineStr">
+      <c r="I8" s="28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I8" s="28" t="inlineStr">
+      <c r="J8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J8" s="28" t="inlineStr">
+      <c r="K8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K8" s="28" t="inlineStr">
+      <c r="L8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L8" s="28" t="inlineStr">
+      <c r="M8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="M8" s="28" t="inlineStr">
+      <c r="N8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="N8" s="28" t="inlineStr">
+      <c r="O8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O8" s="28" t="inlineStr">
+      <c r="P8" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P8" s="28" t="inlineStr">
+      <c r="Q8" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q8" s="28" t="inlineStr">
+      <c r="R8" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="R8" s="28" t="inlineStr">
+      <c r="S8" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="S8" s="28" t="inlineStr">
+      <c r="T8" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T8" s="28" t="inlineStr">
+      <c r="U8" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U8" s="28" t="inlineStr">
+      <c r="V8" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V8" s="28" t="inlineStr">
+      <c r="W8" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="W8" s="28" t="inlineStr">
+      <c r="X8" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="X8" s="28" t="inlineStr">
+      <c r="Y8" s="28" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Y8" s="28" t="inlineStr">
+      <c r="Z8" s="28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="Z8" s="28" t="inlineStr">
+      <c r="AA8" s="28" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="AA8" s="28" t="inlineStr">
+      <c r="AB8" s="28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AB8" s="28" t="inlineStr">
+      <c r="AC8" s="28" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AC8" s="28" t="inlineStr">
+      <c r="AD8" s="28" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AD8" s="28" t="inlineStr">
+      <c r="AE8" s="28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AE8" s="28" t="inlineStr">
+      <c r="AF8" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AF8" s="28" t="inlineStr">
+      <c r="AG8" s="28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="AG8" s="28" t="inlineStr">
+      <c r="AH8" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -30798,36 +30840,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA8"/>
+  <dimension ref="A1:AB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8.4" customWidth="1" min="1" max="1"/>
-    <col width="20.4" customWidth="1" min="2" max="2"/>
-    <col width="15.6" customWidth="1" min="3" max="3"/>
-    <col width="21.6" customWidth="1" min="4" max="4"/>
-    <col width="26.4" customWidth="1" min="5" max="5"/>
-    <col width="19.2" customWidth="1" min="6" max="6"/>
-    <col width="32.4" customWidth="1" min="7" max="7"/>
-    <col width="34.8" customWidth="1" min="8" max="8"/>
-    <col width="39.6" customWidth="1" min="9" max="9"/>
-    <col width="40.8" customWidth="1" min="10" max="10"/>
-    <col width="43.2" customWidth="1" min="11" max="11"/>
-    <col width="21.6" customWidth="1" min="12" max="12"/>
-    <col width="31.2" customWidth="1" min="13" max="13"/>
-    <col width="21.6" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="8.4" customWidth="1" min="2" max="2"/>
+    <col width="20.4" customWidth="1" min="3" max="3"/>
+    <col width="15.6" customWidth="1" min="4" max="4"/>
+    <col width="21.6" customWidth="1" min="5" max="5"/>
+    <col width="26.4" customWidth="1" min="6" max="6"/>
+    <col width="19.2" customWidth="1" min="7" max="7"/>
+    <col width="32.4" customWidth="1" min="8" max="8"/>
+    <col width="34.8" customWidth="1" min="9" max="9"/>
+    <col width="39.6" customWidth="1" min="10" max="10"/>
+    <col width="40.8" customWidth="1" min="11" max="11"/>
+    <col width="43.2" customWidth="1" min="12" max="12"/>
+    <col width="21.6" customWidth="1" min="13" max="13"/>
+    <col width="31.2" customWidth="1" min="14" max="14"/>
     <col width="21.6" customWidth="1" min="15" max="15"/>
-    <col width="24" customWidth="1" min="16" max="16"/>
-    <col width="45.6" customWidth="1" min="17" max="17"/>
-    <col width="46.8" customWidth="1" min="18" max="18"/>
-    <col width="49.2" customWidth="1" min="19" max="19"/>
-    <col width="14.4" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
-    <col width="13.2" customWidth="1" min="22" max="22"/>
-    <col width="32.4" customWidth="1" min="23" max="23"/>
-    <col width="18" customWidth="1" min="24" max="24"/>
-    <col width="45.6" customWidth="1" min="25" max="25"/>
-    <col width="46.8" customWidth="1" min="26" max="26"/>
-    <col width="49.2" customWidth="1" min="27" max="27"/>
+    <col width="21.6" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="45.6" customWidth="1" min="18" max="18"/>
+    <col width="46.8" customWidth="1" min="19" max="19"/>
+    <col width="49.2" customWidth="1" min="20" max="20"/>
+    <col width="14.4" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="13.2" customWidth="1" min="23" max="23"/>
+    <col width="32.4" customWidth="1" min="24" max="24"/>
+    <col width="18" customWidth="1" min="25" max="25"/>
+    <col width="45.6" customWidth="1" min="26" max="26"/>
+    <col width="46.8" customWidth="1" min="27" max="27"/>
+    <col width="49.2" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -30854,135 +30897,140 @@
     <row r="5">
       <c r="A5" s="25" t="inlineStr">
         <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Route departure</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>Responsible</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Loading platform</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Main delivery method</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>Departure days</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
         <is>
           <t>Time of departure - hours</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t>Time of departure - minutes</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="J5" s="25" t="inlineStr">
         <is>
           <t>Transportation lead time - days</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t>Transportation lead time - hours</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="L5" s="25" t="inlineStr">
         <is>
           <t>Transportation lead time - minutes</t>
         </is>
       </c>
-      <c r="L5" s="25" t="inlineStr">
+      <c r="M5" s="25" t="inlineStr">
         <is>
           <t>Forwarding agent</t>
         </is>
       </c>
-      <c r="M5" s="25" t="inlineStr">
+      <c r="N5" s="25" t="inlineStr">
         <is>
           <t>Transportation equipment</t>
         </is>
       </c>
-      <c r="N5" s="25" t="inlineStr">
+      <c r="O5" s="25" t="inlineStr">
         <is>
           <t>Days to deadline</t>
         </is>
       </c>
-      <c r="O5" s="25" t="inlineStr">
+      <c r="P5" s="25" t="inlineStr">
         <is>
           <t>Deadline - hours</t>
         </is>
       </c>
-      <c r="P5" s="25" t="inlineStr">
+      <c r="Q5" s="25" t="inlineStr">
         <is>
           <t>Deadline - minutes</t>
         </is>
       </c>
-      <c r="Q5" s="25" t="inlineStr">
+      <c r="R5" s="25" t="inlineStr">
         <is>
           <t>Stipulated internal lead time - days</t>
         </is>
       </c>
-      <c r="R5" s="25" t="inlineStr">
+      <c r="S5" s="25" t="inlineStr">
         <is>
           <t>Stipulated internal lead time - hours</t>
         </is>
       </c>
-      <c r="S5" s="25" t="inlineStr">
+      <c r="T5" s="25" t="inlineStr">
         <is>
           <t>Stipulated internal lead time - minutes</t>
         </is>
       </c>
-      <c r="T5" s="25" t="inlineStr">
+      <c r="U5" s="25" t="inlineStr">
         <is>
           <t>Valid from</t>
         </is>
       </c>
-      <c r="U5" s="25" t="inlineStr">
+      <c r="V5" s="25" t="inlineStr">
         <is>
           <t>Valid to</t>
         </is>
       </c>
-      <c r="V5" s="25" t="inlineStr">
+      <c r="W5" s="25" t="inlineStr">
         <is>
           <t>Warehouse</t>
         </is>
       </c>
-      <c r="W5" s="25" t="inlineStr">
+      <c r="X5" s="25" t="inlineStr">
         <is>
           <t>Transportation service ID</t>
         </is>
       </c>
-      <c r="X5" s="25" t="inlineStr">
+      <c r="Y5" s="25" t="inlineStr">
         <is>
           <t>Load building</t>
         </is>
       </c>
-      <c r="Y5" s="25" t="inlineStr">
+      <c r="Z5" s="25" t="inlineStr">
         <is>
           <t>Forwarder's arrival lead time - days</t>
         </is>
       </c>
-      <c r="Z5" s="25" t="inlineStr">
+      <c r="AA5" s="25" t="inlineStr">
         <is>
           <t>Forwarder's arrival lead time - hours</t>
         </is>
       </c>
-      <c r="AA5" s="25" t="inlineStr">
+      <c r="AB5" s="25" t="inlineStr">
         <is>
           <t>Forwarder's arrival lead time - minutes</t>
         </is>
@@ -30991,135 +31039,140 @@
     <row r="6">
       <c r="A6" s="26" t="inlineStr">
         <is>
+          <t>DIVI</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
           <t>ROUT</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>RODN</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>RESP</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>LODO</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="F6" s="26" t="inlineStr">
         <is>
           <t>MMDL</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="G6" s="26" t="inlineStr">
         <is>
           <t>DDOW</t>
         </is>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="H6" s="26" t="inlineStr">
         <is>
           <t>DETH</t>
         </is>
       </c>
-      <c r="H6" s="26" t="inlineStr">
+      <c r="I6" s="26" t="inlineStr">
         <is>
           <t>DETM</t>
         </is>
       </c>
-      <c r="I6" s="26" t="inlineStr">
+      <c r="J6" s="26" t="inlineStr">
         <is>
           <t>ARDY</t>
         </is>
       </c>
-      <c r="J6" s="26" t="inlineStr">
+      <c r="K6" s="26" t="inlineStr">
         <is>
           <t>ARHH</t>
         </is>
       </c>
-      <c r="K6" s="26" t="inlineStr">
+      <c r="L6" s="26" t="inlineStr">
         <is>
           <t>ARMM</t>
         </is>
       </c>
-      <c r="L6" s="26" t="inlineStr">
+      <c r="M6" s="26" t="inlineStr">
         <is>
           <t>FWNO</t>
         </is>
       </c>
-      <c r="M6" s="26" t="inlineStr">
+      <c r="N6" s="26" t="inlineStr">
         <is>
           <t>TRCA</t>
         </is>
       </c>
-      <c r="N6" s="26" t="inlineStr">
+      <c r="O6" s="26" t="inlineStr">
         <is>
           <t>LILD</t>
         </is>
       </c>
-      <c r="O6" s="26" t="inlineStr">
+      <c r="P6" s="26" t="inlineStr">
         <is>
           <t>LILH</t>
         </is>
       </c>
-      <c r="P6" s="26" t="inlineStr">
+      <c r="Q6" s="26" t="inlineStr">
         <is>
           <t>LILM</t>
         </is>
       </c>
-      <c r="Q6" s="26" t="inlineStr">
+      <c r="R6" s="26" t="inlineStr">
         <is>
           <t>SILD</t>
         </is>
       </c>
-      <c r="R6" s="26" t="inlineStr">
+      <c r="S6" s="26" t="inlineStr">
         <is>
           <t>SILH</t>
         </is>
       </c>
-      <c r="S6" s="26" t="inlineStr">
+      <c r="T6" s="26" t="inlineStr">
         <is>
           <t>SILM</t>
         </is>
       </c>
-      <c r="T6" s="26" t="inlineStr">
+      <c r="U6" s="26" t="inlineStr">
         <is>
           <t>VFDT</t>
         </is>
       </c>
-      <c r="U6" s="26" t="inlineStr">
+      <c r="V6" s="26" t="inlineStr">
         <is>
           <t>VTDT</t>
         </is>
       </c>
-      <c r="V6" s="26" t="inlineStr">
+      <c r="W6" s="26" t="inlineStr">
         <is>
           <t>WHLO</t>
         </is>
       </c>
-      <c r="W6" s="26" t="inlineStr">
+      <c r="X6" s="26" t="inlineStr">
         <is>
           <t>TSID</t>
         </is>
       </c>
-      <c r="X6" s="26" t="inlineStr">
+      <c r="Y6" s="26" t="inlineStr">
         <is>
           <t>LOBL</t>
         </is>
       </c>
-      <c r="Y6" s="26" t="inlineStr">
+      <c r="Z6" s="26" t="inlineStr">
         <is>
           <t>FWLD</t>
         </is>
       </c>
-      <c r="Z6" s="26" t="inlineStr">
+      <c r="AA6" s="26" t="inlineStr">
         <is>
           <t>FWLH</t>
         </is>
       </c>
-      <c r="AA6" s="26" t="inlineStr">
+      <c r="AB6" s="26" t="inlineStr">
         <is>
           <t>FWLM</t>
         </is>
@@ -31133,130 +31186,135 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="F7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="F7" s="27" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G7" s="27" t="inlineStr">
+      <c r="H7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H7" s="27" t="inlineStr">
+      <c r="I7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I7" s="27" t="inlineStr">
+      <c r="J7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="J7" s="27" t="inlineStr">
+      <c r="K7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K7" s="27" t="inlineStr">
+      <c r="L7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L7" s="27" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="M7" s="27" t="inlineStr">
+      <c r="N7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="N7" s="27" t="inlineStr">
+      <c r="O7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="O7" s="27" t="inlineStr">
+      <c r="P7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P7" s="27" t="inlineStr">
+      <c r="Q7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q7" s="27" t="inlineStr">
+      <c r="R7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R7" s="27" t="inlineStr">
+      <c r="S7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="S7" s="27" t="inlineStr">
+      <c r="T7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="T7" s="27" t="inlineStr">
+      <c r="U7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="U7" s="27" t="inlineStr">
+      <c r="V7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="V7" s="27" t="inlineStr">
+      <c r="W7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="W7" s="27" t="inlineStr">
+      <c r="X7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="X7" s="27" t="inlineStr">
+      <c r="Y7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Y7" s="27" t="inlineStr">
+      <c r="Z7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Z7" s="27" t="inlineStr">
+      <c r="AA7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="AA7" s="27" t="inlineStr">
+      <c r="AB7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -31265,135 +31323,140 @@
     <row r="8">
       <c r="A8" s="28" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="G8" s="28" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G8" s="28" t="inlineStr">
+      <c r="H8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" s="28" t="inlineStr">
+      <c r="I8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="I8" s="28" t="inlineStr">
+      <c r="J8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J8" s="28" t="inlineStr">
+      <c r="K8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K8" s="28" t="inlineStr">
+      <c r="L8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="L8" s="28" t="inlineStr">
+      <c r="M8" s="28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="M8" s="28" t="inlineStr">
+      <c r="N8" s="28" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="N8" s="28" t="inlineStr">
+      <c r="O8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="O8" s="28" t="inlineStr">
+      <c r="P8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P8" s="28" t="inlineStr">
+      <c r="Q8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" s="28" t="inlineStr">
+      <c r="R8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="R8" s="28" t="inlineStr">
+      <c r="S8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="S8" s="28" t="inlineStr">
+      <c r="T8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="T8" s="28" t="inlineStr">
+      <c r="U8" s="28" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="U8" s="28" t="inlineStr">
+      <c r="V8" s="28" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="V8" s="28" t="inlineStr">
+      <c r="W8" s="28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="W8" s="28" t="inlineStr">
+      <c r="X8" s="28" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="X8" s="28" t="inlineStr">
+      <c r="Y8" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y8" s="28" t="inlineStr">
+      <c r="Z8" s="28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Z8" s="28" t="inlineStr">
+      <c r="AA8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="28" t="inlineStr">
+      <c r="AB8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -31413,31 +31476,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V8"/>
+  <dimension ref="A1:W8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="8.4" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="8.4" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="8.4" customWidth="1" min="7" max="7"/>
-    <col width="20.4" customWidth="1" min="8" max="8"/>
-    <col width="21.6" customWidth="1" min="9" max="9"/>
-    <col width="33.6" customWidth="1" min="10" max="10"/>
-    <col width="13.2" customWidth="1" min="11" max="11"/>
-    <col width="31.2" customWidth="1" min="12" max="12"/>
-    <col width="28.8" customWidth="1" min="13" max="13"/>
-    <col width="46.8" customWidth="1" min="14" max="14"/>
-    <col width="48" customWidth="1" min="15" max="15"/>
-    <col width="50" customWidth="1" min="16" max="16"/>
-    <col width="19.2" customWidth="1" min="17" max="17"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="8.4" customWidth="1" min="8" max="8"/>
+    <col width="20.4" customWidth="1" min="9" max="9"/>
+    <col width="21.6" customWidth="1" min="10" max="10"/>
+    <col width="33.6" customWidth="1" min="11" max="11"/>
+    <col width="13.2" customWidth="1" min="12" max="12"/>
+    <col width="31.2" customWidth="1" min="13" max="13"/>
+    <col width="28.8" customWidth="1" min="14" max="14"/>
+    <col width="46.8" customWidth="1" min="15" max="15"/>
+    <col width="48" customWidth="1" min="16" max="16"/>
+    <col width="50" customWidth="1" min="17" max="17"/>
     <col width="19.2" customWidth="1" min="18" max="18"/>
-    <col width="31.2" customWidth="1" min="19" max="19"/>
-    <col width="39.6" customWidth="1" min="20" max="20"/>
-    <col width="24" customWidth="1" min="21" max="21"/>
-    <col width="34.8" customWidth="1" min="22" max="22"/>
+    <col width="19.2" customWidth="1" min="19" max="19"/>
+    <col width="31.2" customWidth="1" min="20" max="20"/>
+    <col width="39.6" customWidth="1" min="21" max="21"/>
+    <col width="24" customWidth="1" min="22" max="22"/>
+    <col width="34.8" customWidth="1" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31464,110 +31528,115 @@
     <row r="5">
       <c r="A5" s="25" t="inlineStr">
         <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
           <t>Priority</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Place</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>Start value 1</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Start value 2</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Start value 3</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>Start value 4</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
         <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t>Route departure</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="J5" s="25" t="inlineStr">
         <is>
           <t>Forwarding agent</t>
         </is>
       </c>
-      <c r="J5" s="25" t="inlineStr">
+      <c r="K5" s="25" t="inlineStr">
         <is>
           <t>Pallet registration number</t>
         </is>
       </c>
-      <c r="K5" s="25" t="inlineStr">
+      <c r="L5" s="25" t="inlineStr">
         <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="L5" s="25" t="inlineStr">
+      <c r="M5" s="25" t="inlineStr">
         <is>
           <t>Earliest collection time</t>
         </is>
       </c>
-      <c r="M5" s="25" t="inlineStr">
+      <c r="N5" s="25" t="inlineStr">
         <is>
           <t>Latest collection time</t>
         </is>
       </c>
-      <c r="N5" s="25" t="inlineStr">
+      <c r="O5" s="25" t="inlineStr">
         <is>
           <t>Local transportation lead time - days</t>
         </is>
       </c>
-      <c r="O5" s="25" t="inlineStr">
+      <c r="P5" s="25" t="inlineStr">
         <is>
           <t>Local transportation lead time - hours</t>
         </is>
       </c>
-      <c r="P5" s="25" t="inlineStr">
+      <c r="Q5" s="25" t="inlineStr">
         <is>
           <t>Local transportation lead time - minutes</t>
         </is>
       </c>
-      <c r="Q5" s="25" t="inlineStr">
+      <c r="R5" s="25" t="inlineStr">
         <is>
           <t>Local distance</t>
         </is>
       </c>
-      <c r="R5" s="25" t="inlineStr">
+      <c r="S5" s="25" t="inlineStr">
         <is>
           <t>Departure days</t>
         </is>
       </c>
-      <c r="S5" s="25" t="inlineStr">
+      <c r="T5" s="25" t="inlineStr">
         <is>
           <t>Transportation equipment</t>
         </is>
       </c>
-      <c r="T5" s="25" t="inlineStr">
+      <c r="U5" s="25" t="inlineStr">
         <is>
           <t>Selection method for departures</t>
         </is>
       </c>
-      <c r="U5" s="25" t="inlineStr">
+      <c r="V5" s="25" t="inlineStr">
         <is>
           <t>Try lower priority</t>
         </is>
       </c>
-      <c r="V5" s="25" t="inlineStr">
+      <c r="W5" s="25" t="inlineStr">
         <is>
           <t>Preliminary route selection</t>
         </is>
@@ -31576,110 +31645,115 @@
     <row r="6">
       <c r="A6" s="26" t="inlineStr">
         <is>
+          <t>DIVI</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
           <t>PREX</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>EDES</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>OBV1</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>OBV2</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="F6" s="26" t="inlineStr">
         <is>
           <t>OBV3</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="G6" s="26" t="inlineStr">
         <is>
           <t>OBV4</t>
         </is>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="H6" s="26" t="inlineStr">
         <is>
           <t>ROUT</t>
         </is>
       </c>
-      <c r="H6" s="26" t="inlineStr">
+      <c r="I6" s="26" t="inlineStr">
         <is>
           <t>RODN</t>
         </is>
       </c>
-      <c r="I6" s="26" t="inlineStr">
+      <c r="J6" s="26" t="inlineStr">
         <is>
           <t>FWNO</t>
         </is>
       </c>
-      <c r="J6" s="26" t="inlineStr">
+      <c r="K6" s="26" t="inlineStr">
         <is>
           <t>PAL1</t>
         </is>
       </c>
-      <c r="K6" s="26" t="inlineStr">
+      <c r="L6" s="26" t="inlineStr">
         <is>
           <t>RFID</t>
         </is>
       </c>
-      <c r="L6" s="26" t="inlineStr">
+      <c r="M6" s="26" t="inlineStr">
         <is>
           <t>CTIE</t>
         </is>
       </c>
-      <c r="M6" s="26" t="inlineStr">
+      <c r="N6" s="26" t="inlineStr">
         <is>
           <t>CTIL</t>
         </is>
       </c>
-      <c r="N6" s="26" t="inlineStr">
+      <c r="O6" s="26" t="inlineStr">
         <is>
           <t>LOLD</t>
         </is>
       </c>
-      <c r="O6" s="26" t="inlineStr">
+      <c r="P6" s="26" t="inlineStr">
         <is>
           <t>LOLH</t>
         </is>
       </c>
-      <c r="P6" s="26" t="inlineStr">
+      <c r="Q6" s="26" t="inlineStr">
         <is>
           <t>LOLM</t>
         </is>
       </c>
-      <c r="Q6" s="26" t="inlineStr">
+      <c r="R6" s="26" t="inlineStr">
         <is>
           <t>LODI</t>
         </is>
       </c>
-      <c r="R6" s="26" t="inlineStr">
+      <c r="S6" s="26" t="inlineStr">
         <is>
           <t>DDOW</t>
         </is>
       </c>
-      <c r="S6" s="26" t="inlineStr">
+      <c r="T6" s="26" t="inlineStr">
         <is>
           <t>TRCA</t>
         </is>
       </c>
-      <c r="T6" s="26" t="inlineStr">
+      <c r="U6" s="26" t="inlineStr">
         <is>
           <t>SEFB</t>
         </is>
       </c>
-      <c r="U6" s="26" t="inlineStr">
+      <c r="V6" s="26" t="inlineStr">
         <is>
           <t>SELP</t>
         </is>
       </c>
-      <c r="V6" s="26" t="inlineStr">
+      <c r="W6" s="26" t="inlineStr">
         <is>
           <t>PRRO</t>
         </is>
@@ -31723,75 +31797,80 @@
       </c>
       <c r="H7" s="27" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I7" s="27" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="I7" s="27" t="inlineStr">
+      <c r="J7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J7" s="27" t="inlineStr">
+      <c r="K7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="K7" s="27" t="inlineStr">
+      <c r="L7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="L7" s="27" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M7" s="27" t="inlineStr">
+      <c r="N7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="N7" s="27" t="inlineStr">
+      <c r="O7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="O7" s="27" t="inlineStr">
+      <c r="P7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="P7" s="27" t="inlineStr">
+      <c r="Q7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="Q7" s="27" t="inlineStr">
+      <c r="R7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R7" s="27" t="inlineStr">
+      <c r="S7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="S7" s="27" t="inlineStr">
+      <c r="T7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="T7" s="27" t="inlineStr">
+      <c r="U7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="U7" s="27" t="inlineStr">
+      <c r="V7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="V7" s="27" t="inlineStr">
+      <c r="W7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -31800,110 +31879,115 @@
     <row r="8">
       <c r="A8" s="28" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="G8" s="28" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="G8" s="28" t="inlineStr">
+      <c r="H8" s="28" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="H8" s="28" t="inlineStr">
+      <c r="I8" s="28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I8" s="28" t="inlineStr">
+      <c r="J8" s="28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J8" s="28" t="inlineStr">
+      <c r="K8" s="28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K8" s="28" t="inlineStr">
+      <c r="L8" s="28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="L8" s="28" t="inlineStr">
+      <c r="M8" s="28" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="M8" s="28" t="inlineStr">
+      <c r="N8" s="28" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="N8" s="28" t="inlineStr">
+      <c r="O8" s="28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O8" s="28" t="inlineStr">
+      <c r="P8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P8" s="28" t="inlineStr">
+      <c r="Q8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" s="28" t="inlineStr">
+      <c r="R8" s="28" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R8" s="28" t="inlineStr">
+      <c r="S8" s="28" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="S8" s="28" t="inlineStr">
+      <c r="T8" s="28" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="T8" s="28" t="inlineStr">
+      <c r="U8" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U8" s="28" t="inlineStr">
+      <c r="V8" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="V8" s="28" t="inlineStr">
+      <c r="W8" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -31923,18 +32007,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8.4" customWidth="1" min="1" max="1"/>
-    <col width="44.4" customWidth="1" min="2" max="2"/>
-    <col width="8.4" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="39.6" customWidth="1" min="5" max="5"/>
-    <col width="40.8" customWidth="1" min="6" max="6"/>
-    <col width="43.2" customWidth="1" min="7" max="7"/>
-    <col width="21.6" customWidth="1" min="8" max="8"/>
-    <col width="25.2" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="8.4" customWidth="1" min="2" max="2"/>
+    <col width="44.4" customWidth="1" min="3" max="3"/>
+    <col width="8.4" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="39.6" customWidth="1" min="6" max="6"/>
+    <col width="40.8" customWidth="1" min="7" max="7"/>
+    <col width="43.2" customWidth="1" min="8" max="8"/>
+    <col width="21.6" customWidth="1" min="9" max="9"/>
+    <col width="25.2" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -31961,45 +32046,50 @@
     <row r="5">
       <c r="A5" s="25" t="inlineStr">
         <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
           <t>Route</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Place sequence number for unloading</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>Place</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Unloading sequence</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Transportation lead time - days</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="G5" s="25" t="inlineStr">
         <is>
           <t>Transportation lead time - hours</t>
         </is>
       </c>
-      <c r="G5" s="25" t="inlineStr">
+      <c r="H5" s="25" t="inlineStr">
         <is>
           <t>Transportation lead time - minutes</t>
         </is>
       </c>
-      <c r="H5" s="25" t="inlineStr">
+      <c r="I5" s="25" t="inlineStr">
         <is>
           <t>Ship-via address</t>
         </is>
       </c>
-      <c r="I5" s="25" t="inlineStr">
+      <c r="J5" s="25" t="inlineStr">
         <is>
           <t>Number of kilometer</t>
         </is>
@@ -32008,45 +32098,50 @@
     <row r="6">
       <c r="A6" s="26" t="inlineStr">
         <is>
+          <t>DIVI</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
           <t>ROUT</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>DESQ</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>EDES</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>ULHC</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="F6" s="26" t="inlineStr">
         <is>
           <t>TPLD</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="G6" s="26" t="inlineStr">
         <is>
           <t>TPLH</t>
         </is>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="H6" s="26" t="inlineStr">
         <is>
           <t>TPLM</t>
         </is>
       </c>
-      <c r="H6" s="26" t="inlineStr">
+      <c r="I6" s="26" t="inlineStr">
         <is>
           <t>ADVI</t>
         </is>
       </c>
-      <c r="I6" s="26" t="inlineStr">
+      <c r="J6" s="26" t="inlineStr">
         <is>
           <t>DIST</t>
         </is>
@@ -32060,40 +32155,45 @@
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="D7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D7" s="27" t="inlineStr">
+      <c r="E7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="E7" s="27" t="inlineStr">
+      <c r="F7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="F7" s="27" t="inlineStr">
+      <c r="G7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G7" s="27" t="inlineStr">
+      <c r="H7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="H7" s="27" t="inlineStr">
+      <c r="I7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I7" s="27" t="inlineStr">
+      <c r="J7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
@@ -32102,45 +32202,50 @@
     <row r="8">
       <c r="A8" s="28" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F8" s="28" t="inlineStr">
+      <c r="G8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G8" s="28" t="inlineStr">
+      <c r="H8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" s="28" t="inlineStr">
+      <c r="I8" s="28" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="I8" s="28" t="inlineStr">
+      <c r="J8" s="28" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -32160,23 +32265,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19.2" customWidth="1" min="1" max="1"/>
-    <col width="13.2" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="15.6" customWidth="1" min="4" max="4"/>
-    <col width="7.199999999999999" customWidth="1" min="5" max="5"/>
-    <col width="13.2" customWidth="1" min="6" max="6"/>
-    <col width="10.8" customWidth="1" min="7" max="7"/>
-    <col width="16.8" customWidth="1" min="8" max="8"/>
-    <col width="16.8" customWidth="1" min="9" max="9"/>
-    <col width="34.8" customWidth="1" min="10" max="10"/>
-    <col width="21.6" customWidth="1" min="11" max="11"/>
-    <col width="22.8" customWidth="1" min="12" max="12"/>
-    <col width="31.2" customWidth="1" min="13" max="13"/>
-    <col width="13.2" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="19.2" customWidth="1" min="2" max="2"/>
+    <col width="13.2" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15.6" customWidth="1" min="5" max="5"/>
+    <col width="7.199999999999999" customWidth="1" min="6" max="6"/>
+    <col width="26.4" customWidth="1" min="7" max="7"/>
+    <col width="26.4" customWidth="1" min="8" max="8"/>
+    <col width="26.4" customWidth="1" min="9" max="9"/>
+    <col width="26.4" customWidth="1" min="10" max="10"/>
+    <col width="26.4" customWidth="1" min="11" max="11"/>
+    <col width="26.4" customWidth="1" min="12" max="12"/>
+    <col width="26.4" customWidth="1" min="13" max="13"/>
+    <col width="26.4" customWidth="1" min="14" max="14"/>
+    <col width="26.4" customWidth="1" min="15" max="15"/>
+    <col width="26.4" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32203,144 +32310,164 @@
     <row r="5">
       <c r="A5" s="25" t="inlineStr">
         <is>
+          <t>Division</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
           <t>Constant value</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Key value</t>
         </is>
       </c>
-      <c r="C5" s="25" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>Language</t>
         </is>
       </c>
-      <c r="D5" s="25" t="inlineStr">
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E5" s="25" t="inlineStr">
+      <c r="F5" s="25" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
-        <is>
-          <t>Time zone</t>
-        </is>
-      </c>
       <c r="G5" s="25" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Reference field TMZO</t>
         </is>
       </c>
       <c r="H5" s="25" t="inlineStr">
         <is>
-          <t>Tariff class</t>
+          <t>Reference field CSCD</t>
         </is>
       </c>
       <c r="I5" s="25" t="inlineStr">
         <is>
-          <t>Freight zone</t>
+          <t>Reference field RACL</t>
         </is>
       </c>
       <c r="J5" s="25" t="inlineStr">
         <is>
-          <t>Responsible must be entered</t>
+          <t>Reference field FRZO</t>
         </is>
       </c>
       <c r="K5" s="25" t="inlineStr">
         <is>
-          <t>Loading platform</t>
+          <t>Reference field MARE</t>
         </is>
       </c>
       <c r="L5" s="25" t="inlineStr">
         <is>
-          <t>Time of departure</t>
+          <t>Reference field MALP</t>
         </is>
       </c>
       <c r="M5" s="25" t="inlineStr">
         <is>
-          <t>Transportation equipment</t>
+          <t>Reference field MADE</t>
         </is>
       </c>
       <c r="N5" s="25" t="inlineStr">
         <is>
-          <t>Time zone</t>
+          <t>Reference field MACA</t>
+        </is>
+      </c>
+      <c r="O5" s="25" t="inlineStr">
+        <is>
+          <t>Reference field TIZO</t>
+        </is>
+      </c>
+      <c r="P5" s="25" t="inlineStr">
+        <is>
+          <t>Reference field PDCL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="26" t="inlineStr">
         <is>
+          <t>DIVI</t>
+        </is>
+      </c>
+      <c r="B6" s="26" t="inlineStr">
+        <is>
           <t>STCO</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="C6" s="26" t="inlineStr">
         <is>
           <t>STKY</t>
         </is>
       </c>
-      <c r="C6" s="26" t="inlineStr">
+      <c r="D6" s="26" t="inlineStr">
         <is>
           <t>LNCD</t>
         </is>
       </c>
-      <c r="D6" s="26" t="inlineStr">
+      <c r="E6" s="26" t="inlineStr">
         <is>
           <t>TX40</t>
         </is>
       </c>
-      <c r="E6" s="26" t="inlineStr">
+      <c r="F6" s="26" t="inlineStr">
         <is>
           <t>TX15</t>
         </is>
       </c>
-      <c r="F6" s="26" t="inlineStr">
+      <c r="G6" s="26" t="inlineStr">
         <is>
           <t>TMZO</t>
         </is>
       </c>
-      <c r="G6" s="26" t="inlineStr">
+      <c r="H6" s="26" t="inlineStr">
         <is>
           <t>CSCD</t>
         </is>
       </c>
-      <c r="H6" s="26" t="inlineStr">
+      <c r="I6" s="26" t="inlineStr">
         <is>
           <t>RACL</t>
         </is>
       </c>
-      <c r="I6" s="26" t="inlineStr">
+      <c r="J6" s="26" t="inlineStr">
         <is>
           <t>FRZO</t>
         </is>
       </c>
-      <c r="J6" s="26" t="inlineStr">
+      <c r="K6" s="26" t="inlineStr">
         <is>
           <t>MARE</t>
         </is>
       </c>
-      <c r="K6" s="26" t="inlineStr">
+      <c r="L6" s="26" t="inlineStr">
         <is>
           <t>MALP</t>
         </is>
       </c>
-      <c r="L6" s="26" t="inlineStr">
+      <c r="M6" s="26" t="inlineStr">
         <is>
           <t>MADE</t>
         </is>
       </c>
-      <c r="M6" s="26" t="inlineStr">
+      <c r="N6" s="26" t="inlineStr">
         <is>
           <t>MACA</t>
         </is>
       </c>
-      <c r="N6" s="26" t="inlineStr">
+      <c r="O6" s="26" t="inlineStr">
         <is>
           <t>TIZO</t>
+        </is>
+      </c>
+      <c r="P6" s="26" t="inlineStr">
+        <is>
+          <t>PDCL</t>
         </is>
       </c>
     </row>
@@ -32372,90 +32499,102 @@
       </c>
       <c r="F7" s="27" t="inlineStr">
         <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G7" s="27" t="inlineStr">
+        <is>
           <t>N</t>
         </is>
       </c>
-      <c r="G7" s="27" t="inlineStr">
+      <c r="H7" s="27" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="H7" s="27" t="inlineStr">
+      <c r="I7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="I7" s="27" t="inlineStr">
+      <c r="J7" s="27" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="J7" s="27" t="inlineStr">
+      <c r="K7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K7" s="27" t="inlineStr">
+      <c r="L7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="L7" s="27" t="inlineStr">
+      <c r="M7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="M7" s="27" t="inlineStr">
+      <c r="N7" s="27" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="N7" s="27" t="inlineStr">
+      <c r="O7" s="27" t="inlineStr">
         <is>
           <t>T</t>
+        </is>
+      </c>
+      <c r="P7" s="27" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="28" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B8" s="28" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="C8" s="28" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D8" s="28" t="inlineStr">
+      <c r="E8" s="28" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E8" s="28" t="inlineStr">
+      <c r="F8" s="28" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="G8" s="28" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="28" t="n">
+      <c r="H8" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="H8" s="28" t="n">
+      <c r="I8" s="28" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="28" t="n">
+      <c r="J8" s="28" t="n">
         <v>5</v>
-      </c>
-      <c r="J8" s="28" t="n">
-        <v>1</v>
       </c>
       <c r="K8" s="28" t="n">
         <v>1</v>
@@ -32467,7 +32606,13 @@
         <v>1</v>
       </c>
       <c r="N8" s="28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" s="28" t="n">
         <v>5</v>
+      </c>
+      <c r="P8" s="28" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
